--- a/russian_data/processed/DATASET-extended.xlsx
+++ b/russian_data/processed/DATASET-extended.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,54 +433,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ret_t</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rpo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rea_t</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta_world</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta_non_rus</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>BRENT</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>cpi_us</t>
+          <t>cpi_rus</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>log_real_brent</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>36526</v>
       </c>
       <c r="B2" t="n">
@@ -490,14 +502,14 @@
         <v>25.59</v>
       </c>
       <c r="H2" t="n">
-        <v>169.3</v>
+        <v>27.88</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.889470638967392</v>
+        <v>-0.08570793572062563</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>36557</v>
       </c>
       <c r="B3" t="n">
@@ -519,14 +531,14 @@
         <v>25.38</v>
       </c>
       <c r="H3" t="n">
-        <v>170</v>
+        <v>28.53</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.90183697476402</v>
+        <v>-0.1169947029391669</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>36586</v>
       </c>
       <c r="B4" t="n">
@@ -548,14 +560,14 @@
         <v>27.7048</v>
       </c>
       <c r="H4" t="n">
-        <v>171</v>
+        <v>28.82</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.820057873122957</v>
+        <v>-0.03946390719167292</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>36617</v>
       </c>
       <c r="B5" t="n">
@@ -577,14 +589,14 @@
         <v>27.47</v>
       </c>
       <c r="H5" t="n">
-        <v>170.9</v>
+        <v>29.01</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.827984090014363</v>
+        <v>-0.05454609802613053</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>36647</v>
       </c>
       <c r="B6" t="n">
@@ -606,14 +618,14 @@
         <v>22.54</v>
       </c>
       <c r="H6" t="n">
-        <v>171.2</v>
+        <v>29.27</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.027540955096011</v>
+        <v>-0.2612715920921644</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>36678</v>
       </c>
       <c r="B7" t="n">
@@ -635,14 +647,14 @@
         <v>27.34</v>
       </c>
       <c r="H7" t="n">
-        <v>172.2</v>
+        <v>29.78</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.840305760697826</v>
+        <v>-0.08548619596005924</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>36708</v>
       </c>
       <c r="B8" t="n">
@@ -664,14 +676,14 @@
         <v>29.6773</v>
       </c>
       <c r="H8" t="n">
-        <v>172.7</v>
+        <v>30.54</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.76117354134191</v>
+        <v>-0.02865485597976436</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>36739</v>
       </c>
       <c r="B9" t="n">
@@ -693,14 +705,14 @@
         <v>28.53</v>
       </c>
       <c r="H9" t="n">
-        <v>172.7</v>
+        <v>31.08</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.800599819927224</v>
+        <v>-0.08560836027403829</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>36770</v>
       </c>
       <c r="B10" t="n">
@@ -722,14 +734,14 @@
         <v>29.43</v>
       </c>
       <c r="H10" t="n">
-        <v>173.6</v>
+        <v>31.39</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.774739239980869</v>
+        <v>-0.0644748086084812</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>36800</v>
       </c>
       <c r="B11" t="n">
@@ -751,14 +763,14 @@
         <v>32.621</v>
       </c>
       <c r="H11" t="n">
-        <v>173.9</v>
+        <v>31.8</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.673524168598016</v>
+        <v>0.02548996297608985</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>36831</v>
       </c>
       <c r="B12" t="n">
@@ -780,14 +792,14 @@
         <v>30.9323</v>
       </c>
       <c r="H12" t="n">
-        <v>174.2</v>
+        <v>32.47</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.728403119024736</v>
+        <v>-0.04851564072108827</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>36861</v>
       </c>
       <c r="B13" t="n">
@@ -809,14 +821,14 @@
         <v>32.52409090909</v>
       </c>
       <c r="H13" t="n">
-        <v>174.6</v>
+        <v>32.97</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.68051656992515</v>
+        <v>-0.01361698360328845</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>36892</v>
       </c>
       <c r="B14" t="n">
@@ -838,14 +850,14 @@
         <v>25.1255</v>
       </c>
       <c r="H14" t="n">
-        <v>175.6</v>
+        <v>33.51</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.944325414522277</v>
+        <v>-0.2879606350704793</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>36923</v>
       </c>
       <c r="B15" t="n">
@@ -867,14 +879,14 @@
         <v>25.63636363636</v>
       </c>
       <c r="H15" t="n">
-        <v>176</v>
+        <v>34.43</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.92647219689855</v>
+        <v>-0.2949164792108312</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>36951</v>
       </c>
       <c r="B16" t="n">
@@ -896,14 +908,14 @@
         <v>27.406</v>
       </c>
       <c r="H16" t="n">
-        <v>176.1</v>
+        <v>35.22</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.860290047978151</v>
+        <v>-0.2508521355440507</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>36982</v>
       </c>
       <c r="B17" t="n">
@@ -925,14 +937,14 @@
         <v>24.39545454545</v>
       </c>
       <c r="H17" t="n">
-        <v>176.4</v>
+        <v>35.87</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.97835731774841</v>
+        <v>-0.3855044657199098</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>37012</v>
       </c>
       <c r="B18" t="n">
@@ -954,14 +966,14 @@
         <v>25.641</v>
       </c>
       <c r="H18" t="n">
-        <v>177.3</v>
+        <v>36.52</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.933650580228172</v>
+        <v>-0.3536674228747771</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>37043</v>
       </c>
       <c r="B19" t="n">
@@ -983,14 +995,14 @@
         <v>28.45047619048</v>
       </c>
       <c r="H19" t="n">
-        <v>177.7</v>
+        <v>37.17</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.831931836925881</v>
+        <v>-0.267337086074436</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>37073</v>
       </c>
       <c r="B20" t="n">
@@ -1012,14 +1024,14 @@
         <v>27.72428571429</v>
       </c>
       <c r="H20" t="n">
-        <v>177.4</v>
+        <v>37.77</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.856098300206634</v>
+        <v>-0.3092063670555203</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>37104</v>
       </c>
       <c r="B21" t="n">
@@ -1041,14 +1053,14 @@
         <v>24.53818181818</v>
       </c>
       <c r="H21" t="n">
-        <v>177.4</v>
+        <v>37.94</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.978176723876265</v>
+        <v>-0.4357756185076544</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>37135</v>
       </c>
       <c r="B22" t="n">
@@ -1070,14 +1082,14 @@
         <v>25.69782608696</v>
       </c>
       <c r="H22" t="n">
-        <v>178.1</v>
+        <v>37.94</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.935938790028245</v>
+        <v>-0.3895995642394965</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>37165</v>
       </c>
       <c r="B23" t="n">
@@ -1099,14 +1111,14 @@
         <v>25.544</v>
       </c>
       <c r="H23" t="n">
-        <v>177.6</v>
+        <v>38.17</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.939131375145589</v>
+        <v>-0.4016474113446575</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>37196</v>
       </c>
       <c r="B24" t="n">
@@ -1128,14 +1140,14 @@
         <v>20.47826086957</v>
       </c>
       <c r="H24" t="n">
-        <v>177.5</v>
+        <v>38.58</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.159606730827969</v>
+        <v>-0.6333701293900815</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>37226</v>
       </c>
       <c r="B25" t="n">
@@ -1157,14 +1169,14 @@
         <v>18.94227272727</v>
       </c>
       <c r="H25" t="n">
-        <v>177.4</v>
+        <v>39.11</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.237010993156531</v>
+        <v>-0.7249821120484752</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>37257</v>
       </c>
       <c r="B26" t="n">
@@ -1186,14 +1198,14 @@
         <v>18.60473684211</v>
       </c>
       <c r="H26" t="n">
-        <v>177.7</v>
+        <v>39.74</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.256680517933433</v>
+        <v>-0.7589420198964976</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>37288</v>
       </c>
       <c r="B27" t="n">
@@ -1215,18 +1227,18 @@
         <v>19.485</v>
       </c>
       <c r="H27" t="n">
-        <v>178</v>
+        <v>40.96</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.212138611501413</v>
+        <v>-0.74295104194058</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>37316</v>
       </c>
       <c r="B28" t="n">
-        <v>13.13691608355108</v>
+        <v>13.13691608355109</v>
       </c>
       <c r="C28" t="n">
         <v>2.524719732166175</v>
@@ -1244,14 +1256,14 @@
         <v>20.2915</v>
       </c>
       <c r="H28" t="n">
-        <v>178.5</v>
+        <v>41.43</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.174386522071142</v>
+        <v>-0.7138031769407593</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>37347</v>
       </c>
       <c r="B29" t="n">
@@ -1273,14 +1285,14 @@
         <v>23.6905</v>
       </c>
       <c r="H29" t="n">
-        <v>179.3</v>
+        <v>41.88</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.023986256711242</v>
+        <v>-0.5697342621024908</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>37377</v>
       </c>
       <c r="B30" t="n">
@@ -1302,14 +1314,14 @@
         <v>25.65409090909</v>
       </c>
       <c r="H30" t="n">
-        <v>179.5</v>
+        <v>42.37</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.945472159395536</v>
+        <v>-0.5017375161056701</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>37408</v>
       </c>
       <c r="B31" t="n">
@@ -1331,14 +1343,14 @@
         <v>25.38727272727</v>
       </c>
       <c r="H31" t="n">
-        <v>179.6</v>
+        <v>43.08</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.956484181152529</v>
+        <v>-0.5288108775726168</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>37438</v>
       </c>
       <c r="B32" t="n">
@@ -1360,14 +1372,14 @@
         <v>24.12789473684</v>
       </c>
       <c r="H32" t="n">
-        <v>180</v>
+        <v>43.31</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.009588221771463</v>
+        <v>-0.5850149261077879</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>37469</v>
       </c>
       <c r="B33" t="n">
@@ -1389,14 +1401,14 @@
         <v>25.76782608696</v>
       </c>
       <c r="H33" t="n">
-        <v>180.5</v>
+        <v>43.62</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.946604114953402</v>
+        <v>-0.5263890979539489</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>37500</v>
       </c>
       <c r="B34" t="n">
@@ -1418,14 +1430,14 @@
         <v>26.63285714286</v>
       </c>
       <c r="H34" t="n">
-        <v>180.8</v>
+        <v>43.66</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.915245763505912</v>
+        <v>-0.4942866666696335</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>37530</v>
       </c>
       <c r="B35" t="n">
@@ -1447,14 +1459,14 @@
         <v>28.34238095238</v>
       </c>
       <c r="H35" t="n">
-        <v>181.2</v>
+        <v>43.84</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.855243149029862</v>
+        <v>-0.4361883980607431</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>37561</v>
       </c>
       <c r="B36" t="n">
@@ -1476,14 +1488,14 @@
         <v>27.54869565217</v>
       </c>
       <c r="H36" t="n">
-        <v>181.5</v>
+        <v>44.3</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.8853004639756</v>
+        <v>-0.4750294873217844</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>37591</v>
       </c>
       <c r="B37" t="n">
@@ -1505,14 +1517,14 @@
         <v>24.18476190476</v>
       </c>
       <c r="H37" t="n">
-        <v>181.8</v>
+        <v>45.02</v>
       </c>
       <c r="I37" t="n">
-        <v>-2.01718442026529</v>
+        <v>-0.6213840740004977</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>37622</v>
       </c>
       <c r="B38" t="n">
@@ -1534,14 +1546,14 @@
         <v>28.52095238095</v>
       </c>
       <c r="H38" t="n">
-        <v>182.6</v>
+        <v>45.71</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.856658979730877</v>
+        <v>-0.4716781039136619</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>37653</v>
       </c>
       <c r="B39" t="n">
@@ -1563,14 +1575,14 @@
         <v>31.24666666667</v>
       </c>
       <c r="H39" t="n">
-        <v>183.6</v>
+        <v>46.81</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.770846774359833</v>
+        <v>-0.4041841514854223</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>37681</v>
       </c>
       <c r="B40" t="n">
@@ -1592,14 +1604,14 @@
         <v>32.6485</v>
       </c>
       <c r="H40" t="n">
-        <v>183.9</v>
+        <v>47.57</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.728593218750237</v>
+        <v>-0.3764033975841516</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>37712</v>
       </c>
       <c r="B41" t="n">
@@ -1621,14 +1633,14 @@
         <v>30.33904761905</v>
       </c>
       <c r="H41" t="n">
-        <v>183.2</v>
+        <v>48.07</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.798142869087543</v>
+        <v>-0.4602226987533822</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>37742</v>
       </c>
       <c r="B42" t="n">
@@ -1650,14 +1662,14 @@
         <v>25.016</v>
       </c>
       <c r="H42" t="n">
-        <v>182.9</v>
+        <v>48.56</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.98942393524128</v>
+        <v>-0.6632845265957026</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>37773</v>
       </c>
       <c r="B43" t="n">
@@ -1679,14 +1691,14 @@
         <v>25.8095</v>
       </c>
       <c r="H43" t="n">
-        <v>183.1</v>
+        <v>48.95</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.959289810473892</v>
+        <v>-0.6400567277699469</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>37803</v>
       </c>
       <c r="B44" t="n">
@@ -1708,14 +1720,14 @@
         <v>27.54571428571</v>
       </c>
       <c r="H44" t="n">
-        <v>183.7</v>
+        <v>49.34</v>
       </c>
       <c r="I44" t="n">
-        <v>-1.897457030040315</v>
+        <v>-0.5828881489204454</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>37834</v>
       </c>
       <c r="B45" t="n">
@@ -1737,14 +1749,14 @@
         <v>28.39826086957</v>
       </c>
       <c r="H45" t="n">
-        <v>184.5</v>
+        <v>49.69</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.871321557175454</v>
+        <v>-0.5594757993091015</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>37865</v>
       </c>
       <c r="B46" t="n">
@@ -1766,14 +1778,14 @@
         <v>29.82571428571</v>
       </c>
       <c r="H46" t="n">
-        <v>185.1</v>
+        <v>49.49</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.825525302654757</v>
+        <v>-0.5063997120390993</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>37895</v>
       </c>
       <c r="B47" t="n">
@@ -1795,14 +1807,14 @@
         <v>27.09818181818</v>
       </c>
       <c r="H47" t="n">
-        <v>184.9</v>
+        <v>49.66</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.920348504338238</v>
+        <v>-0.6057331460251802</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>37926</v>
       </c>
       <c r="B48" t="n">
@@ -1824,14 +1836,14 @@
         <v>29.59043478261</v>
       </c>
       <c r="H48" t="n">
-        <v>185</v>
+        <v>50.15</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.832904665208424</v>
+        <v>-0.5275673545380442</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>37956</v>
       </c>
       <c r="B49" t="n">
@@ -1853,14 +1865,14 @@
         <v>28.772</v>
       </c>
       <c r="H49" t="n">
-        <v>185.5</v>
+        <v>50.63</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.86365219004238</v>
+        <v>-0.5651415939767079</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>37987</v>
       </c>
       <c r="B50" t="n">
@@ -1882,14 +1894,14 @@
         <v>29.92666666667</v>
       </c>
       <c r="H50" t="n">
-        <v>186.3</v>
+        <v>51.19</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.828608332921755</v>
+        <v>-0.536794255783704</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>38018</v>
       </c>
       <c r="B51" t="n">
@@ -1911,14 +1923,14 @@
         <v>31.17523809524</v>
       </c>
       <c r="H51" t="n">
-        <v>186.7</v>
+        <v>52.09</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.789878921633355</v>
+        <v>-0.5133488628427791</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>38047</v>
       </c>
       <c r="B52" t="n">
@@ -1940,14 +1952,14 @@
         <v>30.866</v>
       </c>
       <c r="H52" t="n">
-        <v>187.1</v>
+        <v>52.6</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.801987978801404</v>
+        <v>-0.5330608652650244</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>38078</v>
       </c>
       <c r="B53" t="n">
@@ -1969,14 +1981,14 @@
         <v>33.79913043478</v>
       </c>
       <c r="H53" t="n">
-        <v>187.4</v>
+        <v>53</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.712810294427945</v>
+        <v>-0.4498568381757453</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>38108</v>
       </c>
       <c r="B54" t="n">
@@ -1998,14 +2010,14 @@
         <v>33.36227272727</v>
       </c>
       <c r="H54" t="n">
-        <v>188.2</v>
+        <v>53.52</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.730079524665047</v>
+        <v>-0.4726297133337405</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>38139</v>
       </c>
       <c r="B55" t="n">
@@ -2027,14 +2039,14 @@
         <v>37.91631578947</v>
       </c>
       <c r="H55" t="n">
-        <v>188.9</v>
+        <v>53.92</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.605836259291419</v>
+        <v>-0.3521199513880071</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>38169</v>
       </c>
       <c r="B56" t="n">
@@ -2056,14 +2068,14 @@
         <v>35.19136363636</v>
       </c>
       <c r="H56" t="n">
-        <v>189.1</v>
+        <v>54.34</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.681475274403673</v>
+        <v>-0.4344599027374625</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>38200</v>
       </c>
       <c r="B57" t="n">
@@ -2085,14 +2097,14 @@
         <v>38.37045454545</v>
       </c>
       <c r="H57" t="n">
-        <v>189.2</v>
+        <v>54.84</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.595516906053009</v>
+        <v>-0.3571321041293456</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>38231</v>
       </c>
       <c r="B58" t="n">
@@ -2114,14 +2126,14 @@
         <v>43.03</v>
       </c>
       <c r="H58" t="n">
-        <v>189.8</v>
+        <v>55.07</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.484073339325319</v>
+        <v>-0.2467075564238819</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>38261</v>
       </c>
       <c r="B59" t="n">
@@ -2143,14 +2155,14 @@
         <v>43.38136363636</v>
       </c>
       <c r="H59" t="n">
-        <v>190.8</v>
+        <v>55.31</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.481195819430864</v>
+        <v>-0.2429237844232639</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>38292</v>
       </c>
       <c r="B60" t="n">
@@ -2172,14 +2184,14 @@
         <v>49.8180952381</v>
       </c>
       <c r="H60" t="n">
-        <v>191.7</v>
+        <v>55.94</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.347553373824814</v>
+        <v>-0.1159014115470294</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>38322</v>
       </c>
       <c r="B61" t="n">
@@ -2201,14 +2213,14 @@
         <v>43.05363636364</v>
       </c>
       <c r="H61" t="n">
-        <v>191.7</v>
+        <v>56.56</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.493484954367875</v>
+        <v>-0.2728553259045943</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B62" t="n">
@@ -2230,14 +2242,14 @@
         <v>39.64428571429</v>
       </c>
       <c r="H62" t="n">
-        <v>191.6</v>
+        <v>57.2</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.575463046018722</v>
+        <v>-0.3666070788677143</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B63" t="n">
@@ -2259,14 +2271,14 @@
         <v>44.28333333333</v>
       </c>
       <c r="H63" t="n">
-        <v>192.4</v>
+        <v>58.7</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.468968154693969</v>
+        <v>-0.2818313432964135</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B64" t="n">
@@ -2288,14 +2300,14 @@
         <v>45.557</v>
       </c>
       <c r="H64" t="n">
-        <v>193.1</v>
+        <v>59.42</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.444243900257927</v>
+        <v>-0.2656665808579208</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B65" t="n">
@@ -2317,14 +2329,14 @@
         <v>53.08409090909</v>
       </c>
       <c r="H65" t="n">
-        <v>193.7</v>
+        <v>60.22</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.294433293287798</v>
+        <v>-0.1261272459284348</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B66" t="n">
@@ -2346,14 +2358,14 @@
         <v>51.85714285714</v>
       </c>
       <c r="H66" t="n">
-        <v>193.6</v>
+        <v>60.89</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.317301489632995</v>
+        <v>-0.1605762724110007</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B67" t="n">
@@ -2375,14 +2387,14 @@
         <v>48.66590909091</v>
       </c>
       <c r="H67" t="n">
-        <v>193.7</v>
+        <v>61.38</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.381331804119022</v>
+        <v>-0.232105282897662</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B68" t="n">
@@ -2404,14 +2416,14 @@
         <v>54.30681818182</v>
       </c>
       <c r="H68" t="n">
-        <v>194.9</v>
+        <v>61.77</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.277836822413529</v>
+        <v>-0.128768025607823</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B69" t="n">
@@ -2433,14 +2445,14 @@
         <v>57.57904761905</v>
       </c>
       <c r="H69" t="n">
-        <v>196.1</v>
+        <v>62.06</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.225465988289655</v>
+        <v>-0.0749429141075888</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B70" t="n">
@@ -2462,14 +2474,14 @@
         <v>64.09</v>
       </c>
       <c r="H70" t="n">
-        <v>198.8</v>
+        <v>61.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.132010948706339</v>
+        <v>0.03363794854211921</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B71" t="n">
@@ -2491,14 +2503,14 @@
         <v>62.98181818182</v>
       </c>
       <c r="H71" t="n">
-        <v>199.1</v>
+        <v>62.12</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.150961126620267</v>
+        <v>0.01377808616939813</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B72" t="n">
@@ -2520,14 +2532,14 @@
         <v>58.5219047619</v>
       </c>
       <c r="H72" t="n">
-        <v>198.1</v>
+        <v>62.47</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.219370829177638</v>
+        <v>-0.06528531697861162</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B73" t="n">
@@ -2549,14 +2561,14 @@
         <v>55.535</v>
       </c>
       <c r="H73" t="n">
-        <v>198.1</v>
+        <v>62.93</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.271758501085422</v>
+        <v>-0.1250095449197595</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B74" t="n">
@@ -2578,14 +2590,14 @@
         <v>56.7475</v>
       </c>
       <c r="H74" t="n">
-        <v>199.3</v>
+        <v>63.44</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.256199624691029</v>
+        <v>-0.1114829747988733</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B75" t="n">
@@ -2607,14 +2619,14 @@
         <v>63.57428571429</v>
       </c>
       <c r="H75" t="n">
-        <v>199.4</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.143103781606462</v>
+        <v>-0.0220243359849821</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B76" t="n">
@@ -2636,18 +2648,18 @@
         <v>59.923</v>
       </c>
       <c r="H76" t="n">
-        <v>199.7</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.203755835710429</v>
+        <v>-0.09765438133045379</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B77" t="n">
-        <v>12.67788644118132</v>
+        <v>12.67788644118133</v>
       </c>
       <c r="C77" t="n">
         <v>3.43708444913175</v>
@@ -2665,14 +2677,14 @@
         <v>62.25304347826</v>
       </c>
       <c r="H77" t="n">
-        <v>200.7</v>
+        <v>66.61</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.170603830435583</v>
+        <v>-0.06764729105837919</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B78" t="n">
@@ -2694,14 +2706,14 @@
         <v>70.44210526316</v>
       </c>
       <c r="H78" t="n">
-        <v>201.3</v>
+        <v>66.84</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.050005162139542</v>
+        <v>0.05248946677901056</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B79" t="n">
@@ -2723,14 +2735,14 @@
         <v>70.18727272727</v>
       </c>
       <c r="H79" t="n">
-        <v>201.8</v>
+        <v>67.16</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.056110113505947</v>
+        <v>0.0440891622042221</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B80" t="n">
@@ -2752,14 +2764,14 @@
         <v>68.85772727273</v>
       </c>
       <c r="H80" t="n">
-        <v>202.9</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.0806707945092</v>
+        <v>0.02213954946619534</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B81" t="n">
@@ -2781,14 +2793,14 @@
         <v>73.89714285714</v>
       </c>
       <c r="H81" t="n">
-        <v>203.8</v>
+        <v>67.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.014464955866853</v>
+        <v>0.08611196997542159</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B82" t="n">
@@ -2810,14 +2822,14 @@
         <v>73.61217391304</v>
       </c>
       <c r="H82" t="n">
-        <v>202.8</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.013409853233159</v>
+        <v>0.08033265528065847</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B83" t="n">
@@ -2839,14 +2851,14 @@
         <v>62.7719047619</v>
       </c>
       <c r="H83" t="n">
-        <v>201.9</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.168264928350185</v>
+        <v>-0.07985303856976156</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B84" t="n">
@@ -2868,14 +2880,14 @@
         <v>58.38</v>
       </c>
       <c r="H84" t="n">
-        <v>202</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.241294331975237</v>
+        <v>-0.1551779012837882</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B85" t="n">
@@ -2897,14 +2909,14 @@
         <v>58.48318181818</v>
       </c>
       <c r="H85" t="n">
-        <v>203.1</v>
+        <v>68.61</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.244959245969304</v>
+        <v>-0.1596990740857649</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B86" t="n">
@@ -2926,14 +2938,14 @@
         <v>62.31473684211</v>
       </c>
       <c r="H86" t="n">
-        <v>203.437</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.183158430399547</v>
+        <v>-0.1040801138677425</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B87" t="n">
@@ -2955,14 +2967,14 @@
         <v>54.29909090909</v>
       </c>
       <c r="H87" t="n">
-        <v>204.226</v>
+        <v>70.31</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.32471973898208</v>
+        <v>-0.2584065514170386</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B88" t="n">
@@ -2984,14 +2996,14 @@
         <v>57.757</v>
       </c>
       <c r="H88" t="n">
-        <v>205.288</v>
+        <v>71.09</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.268169317091791</v>
+        <v>-0.2077021257638725</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B89" t="n">
@@ -3013,14 +3025,14 @@
         <v>62.14363636364</v>
       </c>
       <c r="H89" t="n">
-        <v>205.904</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.197961619611542</v>
+        <v>-0.140388878920537</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B90" t="n">
@@ -3042,14 +3054,14 @@
         <v>67.39842105263</v>
       </c>
       <c r="H90" t="n">
-        <v>206.755</v>
+        <v>71.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.12091292628322</v>
+        <v>-0.0649327990383517</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B91" t="n">
@@ -3071,14 +3083,14 @@
         <v>67.47608695652001</v>
       </c>
       <c r="H91" t="n">
-        <v>207.234</v>
+        <v>72.37</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.122075321787511</v>
+        <v>-0.0700185810778553</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B92" t="n">
@@ -3100,14 +3112,14 @@
         <v>71.31619047619</v>
       </c>
       <c r="H92" t="n">
-        <v>207.603</v>
+        <v>73.06</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.068504225009455</v>
+        <v>-0.02415764432221845</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B93" t="n">
@@ -3129,14 +3141,14 @@
         <v>77.20409090909</v>
       </c>
       <c r="H93" t="n">
-        <v>207.667</v>
+        <v>73.7</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.9894833885773489</v>
+        <v>0.04644964748185121</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B94" t="n">
@@ -3158,14 +3170,14 @@
         <v>70.79652173913</v>
       </c>
       <c r="H94" t="n">
-        <v>208.547</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.080354563985464</v>
+        <v>-0.04100670773387272</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B95" t="n">
@@ -3187,14 +3199,14 @@
         <v>77.127</v>
       </c>
       <c r="H95" t="n">
-        <v>209.19</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.9977895160830164</v>
+        <v>0.03666974091184905</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B96" t="n">
@@ -3216,14 +3228,14 @@
         <v>82.85782608696</v>
       </c>
       <c r="H96" t="n">
-        <v>210.834</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.933944893655644</v>
+        <v>0.09206682129562971</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B97" t="n">
@@ -3245,14 +3257,14 @@
         <v>92.52818181818</v>
       </c>
       <c r="H97" t="n">
-        <v>211.445</v>
+        <v>76.5</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.8264516509657867</v>
+        <v>0.1902225255885748</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B98" t="n">
@@ -3274,14 +3286,14 @@
         <v>91.45</v>
       </c>
       <c r="H98" t="n">
-        <v>212.174</v>
+        <v>77.36</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.8416143179171502</v>
+        <v>0.1673225236918361</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B99" t="n">
@@ -3303,14 +3315,14 @@
         <v>91.92045454545</v>
       </c>
       <c r="H99" t="n">
-        <v>212.687</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.8388980228517822</v>
+        <v>0.1495787922126759</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B100" t="n">
@@ -3332,14 +3344,14 @@
         <v>94.81666666667</v>
       </c>
       <c r="H100" t="n">
-        <v>213.448</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.8114480407556419</v>
+        <v>0.1686693484542685</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B101" t="n">
@@ -3361,14 +3373,14 @@
         <v>103.2775</v>
       </c>
       <c r="H101" t="n">
-        <v>213.942</v>
+        <v>81.06</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7282854100461442</v>
+        <v>0.2422299190034254</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B102" t="n">
@@ -3390,14 +3402,14 @@
         <v>110.18772727273</v>
       </c>
       <c r="H102" t="n">
-        <v>215.208</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.6694194795619621</v>
+        <v>0.292908573591852</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B103" t="n">
@@ -3419,14 +3431,14 @@
         <v>123.93619047619</v>
       </c>
       <c r="H103" t="n">
-        <v>217.463</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.5622618808923203</v>
+        <v>0.3970782238299302</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B104" t="n">
@@ -3448,14 +3460,14 @@
         <v>133.04857142857</v>
       </c>
       <c r="H104" t="n">
-        <v>219.016</v>
+        <v>84.13</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4984305262445385</v>
+        <v>0.4583510387012657</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B105" t="n">
@@ -3477,14 +3489,14 @@
         <v>133.87304347826</v>
       </c>
       <c r="H105" t="n">
-        <v>218.69</v>
+        <v>84.56</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4907632877805872</v>
+        <v>0.459430572557662</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B106" t="n">
@@ -3506,14 +3518,14 @@
         <v>113.84904761905</v>
       </c>
       <c r="H106" t="n">
-        <v>218.877</v>
+        <v>84.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6536365009508804</v>
+        <v>0.2938705874748448</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B107" t="n">
@@ -3535,14 +3547,14 @@
         <v>99.06409090909</v>
       </c>
       <c r="H107" t="n">
-        <v>216.995</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7841072882075819</v>
+        <v>0.1467829207940019</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B108" t="n">
@@ -3564,14 +3576,14 @@
         <v>72.84260869565</v>
       </c>
       <c r="H108" t="n">
-        <v>213.153</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="I108" t="n">
-        <v>-1.073709149436024</v>
+        <v>-0.1697602526783752</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B109" t="n">
@@ -3593,14 +3605,14 @@
         <v>53.241</v>
       </c>
       <c r="H109" t="n">
-        <v>211.398</v>
+        <v>87.03</v>
       </c>
       <c r="I109" t="n">
-        <v>-1.378913836432909</v>
+        <v>-0.4914241105808848</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B110" t="n">
@@ -3622,14 +3634,14 @@
         <v>41.58090909091</v>
       </c>
       <c r="H110" t="n">
-        <v>211.933</v>
+        <v>87.63</v>
       </c>
       <c r="I110" t="n">
-        <v>-1.628629041136604</v>
+        <v>-0.7454822592186492</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B111" t="n">
@@ -3651,18 +3663,18 @@
         <v>44.86</v>
       </c>
       <c r="H111" t="n">
-        <v>212.705</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="I111" t="n">
-        <v>-1.556359700125097</v>
+        <v>-0.6930357164791299</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B112" t="n">
-        <v>13.2460749040845</v>
+        <v>13.24607490408451</v>
       </c>
       <c r="C112" t="n">
         <v>3.07402318029276</v>
@@ -3680,14 +3692,14 @@
         <v>43.2425</v>
       </c>
       <c r="H112" t="n">
-        <v>212.495</v>
+        <v>91.19</v>
       </c>
       <c r="I112" t="n">
-        <v>-1.592094650739944</v>
+        <v>-0.7461214340096327</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B113" t="n">
@@ -3709,14 +3721,14 @@
         <v>46.83909090909</v>
       </c>
       <c r="H113" t="n">
-        <v>212.709</v>
+        <v>92.39</v>
       </c>
       <c r="I113" t="n">
-        <v>-1.513206904317955</v>
+        <v>-0.6793006175725256</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B114" t="n">
@@ -3738,18 +3750,18 @@
         <v>50.84523809524</v>
       </c>
       <c r="H114" t="n">
-        <v>213.022</v>
+        <v>93.02</v>
       </c>
       <c r="I114" t="n">
-        <v>-1.43260897476254</v>
+        <v>-0.6040280517977603</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B115" t="n">
-        <v>-15.08860714692284</v>
+        <v>-15.08860714692285</v>
       </c>
       <c r="C115" t="n">
         <v>3.430754526529753</v>
@@ -3767,14 +3779,14 @@
         <v>57.94095238095</v>
       </c>
       <c r="H115" t="n">
-        <v>214.79</v>
+        <v>93.55</v>
       </c>
       <c r="I115" t="n">
-        <v>-1.310236377044681</v>
+        <v>-0.4790716231486085</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B116" t="n">
@@ -3796,14 +3808,14 @@
         <v>68.61681818181999</v>
       </c>
       <c r="H116" t="n">
-        <v>214.726</v>
+        <v>94.12</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.140825129076423</v>
+        <v>-0.3160328961745682</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B117" t="n">
@@ -3825,14 +3837,14 @@
         <v>64.91</v>
       </c>
       <c r="H117" t="n">
-        <v>215.445</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I117" t="n">
-        <v>-1.199703961506518</v>
+        <v>-0.3778178961926333</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B118" t="n">
@@ -3854,14 +3866,14 @@
         <v>72.50476190476</v>
       </c>
       <c r="H118" t="n">
-        <v>215.861</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I118" t="n">
-        <v>-1.090982440870069</v>
+        <v>-0.2671673500893474</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B119" t="n">
@@ -3883,14 +3895,14 @@
         <v>67.68681818182</v>
       </c>
       <c r="H119" t="n">
-        <v>216.509</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>-1.162740665336278</v>
+        <v>-0.3356113329647439</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B120" t="n">
@@ -3912,14 +3924,14 @@
         <v>73.19409090908999</v>
       </c>
       <c r="H120" t="n">
-        <v>217.234</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>-1.087860421139099</v>
+        <v>-0.2573880922226337</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B121" t="n">
@@ -3941,14 +3953,14 @@
         <v>77.03666666667</v>
       </c>
       <c r="H121" t="n">
-        <v>217.347</v>
+        <v>94.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.037213655729833</v>
+        <v>-0.2090689382710824</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B122" t="n">
@@ -3970,14 +3982,14 @@
         <v>74.66954545455</v>
       </c>
       <c r="H122" t="n">
-        <v>217.488</v>
+        <v>95.34</v>
       </c>
       <c r="I122" t="n">
-        <v>-1.069071358954329</v>
+        <v>-0.2443771321381165</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B123" t="n">
@@ -3999,14 +4011,14 @@
         <v>76.373</v>
       </c>
       <c r="H123" t="n">
-        <v>217.281</v>
+        <v>96.91</v>
       </c>
       <c r="I123" t="n">
-        <v>-1.04556221614664</v>
+        <v>-0.2381534821769522</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B124" t="n">
@@ -4028,14 +4040,14 @@
         <v>74.312</v>
       </c>
       <c r="H124" t="n">
-        <v>217.353</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>-1.073250313876824</v>
+        <v>-0.2740384457567888</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B125" t="n">
@@ -4057,14 +4069,14 @@
         <v>79.27478260869999</v>
       </c>
       <c r="H125" t="n">
-        <v>217.403</v>
+        <v>98.36</v>
       </c>
       <c r="I125" t="n">
-        <v>-1.008832695862094</v>
+        <v>-0.2157141391701662</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B126" t="n">
@@ -4086,14 +4098,14 @@
         <v>84.97857142857001</v>
       </c>
       <c r="H126" t="n">
-        <v>217.29</v>
+        <v>98.64</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9388337430081393</v>
+        <v>-0.1490777349888832</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B127" t="n">
@@ -4115,14 +4127,14 @@
         <v>76.25095238095</v>
       </c>
       <c r="H127" t="n">
-        <v>217.199</v>
+        <v>99.14</v>
       </c>
       <c r="I127" t="n">
-        <v>-1.046784078346131</v>
+        <v>-0.2625030869409422</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B128" t="n">
@@ -4144,14 +4156,14 @@
         <v>74.83818181818</v>
       </c>
       <c r="H128" t="n">
-        <v>217.605</v>
+        <v>99.52</v>
       </c>
       <c r="I128" t="n">
-        <v>-1.0673532858002</v>
+        <v>-0.2850304221320945</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B129" t="n">
@@ -4173,14 +4185,14 @@
         <v>74.73545454545</v>
       </c>
       <c r="H129" t="n">
-        <v>217.923</v>
+        <v>99.88</v>
       </c>
       <c r="I129" t="n">
-        <v>-1.070187184070859</v>
+        <v>-0.2900148600962176</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B130" t="n">
@@ -4202,14 +4214,14 @@
         <v>76.69318181817999</v>
       </c>
       <c r="H130" t="n">
-        <v>218.275</v>
+        <v>100.43</v>
       </c>
       <c r="I130" t="n">
-        <v>-1.045942925431695</v>
+        <v>-0.2696481571400717</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B131" t="n">
@@ -4231,14 +4243,14 @@
         <v>77.78681818182</v>
       </c>
       <c r="H131" t="n">
-        <v>219.035</v>
+        <v>101.27</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.035259549679845</v>
+        <v>-0.263818232625372</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B132" t="n">
@@ -4260,14 +4272,14 @@
         <v>82.91809523809999</v>
       </c>
       <c r="H132" t="n">
-        <v>219.59</v>
+        <v>101.78</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.973908855033514</v>
+        <v>-0.2049603049363</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B133" t="n">
@@ -4289,14 +4301,14 @@
         <v>85.67</v>
       </c>
       <c r="H133" t="n">
-        <v>220.472</v>
+        <v>102.6</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.9452679967207969</v>
+        <v>-0.1803352267607163</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B134" t="n">
@@ -4318,14 +4330,14 @@
         <v>91.79652173913</v>
       </c>
       <c r="H134" t="n">
-        <v>221.187</v>
+        <v>103.71</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.879434090220899</v>
+        <v>-0.1220241352449865</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B135" t="n">
@@ -4347,14 +4359,14 @@
         <v>96.29428571429</v>
       </c>
       <c r="H135" t="n">
-        <v>221.898</v>
+        <v>106.17</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.8348088381625427</v>
+        <v>-0.09763260435904364</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B136" t="n">
@@ -4376,14 +4388,14 @@
         <v>103.9555</v>
       </c>
       <c r="H136" t="n">
-        <v>223.046</v>
+        <v>107</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7634151052573932</v>
+        <v>-0.02886591150466167</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B137" t="n">
@@ -4405,14 +4417,14 @@
         <v>114.44130434783</v>
       </c>
       <c r="H137" t="n">
-        <v>224.093</v>
+        <v>107.66</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.6719990784900602</v>
+        <v>0.06108395264082134</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B138" t="n">
@@ -4434,14 +4446,14 @@
         <v>123.07</v>
       </c>
       <c r="H138" t="n">
-        <v>224.806</v>
+        <v>108.12</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.6024845088705675</v>
+        <v>0.1295115777759985</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B139" t="n">
@@ -4463,14 +4475,14 @@
         <v>114.45818181818</v>
       </c>
       <c r="H139" t="n">
-        <v>224.806</v>
+        <v>108.64</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.6750282760665263</v>
+        <v>0.05216986817790037</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B140" t="n">
@@ -4492,14 +4504,14 @@
         <v>113.75772727273</v>
       </c>
       <c r="H140" t="n">
-        <v>225.395</v>
+        <v>108.89</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6837834309817392</v>
+        <v>0.04373278923376756</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B141" t="n">
@@ -4521,14 +4533,14 @@
         <v>116.46</v>
       </c>
       <c r="H141" t="n">
-        <v>226.106</v>
+        <v>108.88</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6634560494534139</v>
+        <v>0.06730150806576329</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B142" t="n">
@@ -4550,18 +4562,18 @@
         <v>110.08130434783</v>
       </c>
       <c r="H142" t="n">
-        <v>226.597</v>
+        <v>108.62</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.721953886113412</v>
+        <v>0.01336367059816013</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B143" t="n">
-        <v>9.26176652574722</v>
+        <v>9.261766525747221</v>
       </c>
       <c r="C143" t="n">
         <v>3.806196866255272</v>
@@ -4579,14 +4591,14 @@
         <v>110.87909090909</v>
       </c>
       <c r="H143" t="n">
-        <v>226.75</v>
+        <v>108.58</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.7154077524591074</v>
+        <v>0.02095310805883432</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B144" t="n">
@@ -4608,14 +4620,14 @@
         <v>109.46857142857</v>
       </c>
       <c r="H144" t="n">
-        <v>227.169</v>
+        <v>109.1</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.730056744734167</v>
+        <v>0.003372596302549269</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B145" t="n">
@@ -4637,14 +4649,14 @@
         <v>110.50409090909</v>
       </c>
       <c r="H145" t="n">
-        <v>227.223</v>
+        <v>109.56</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.7208793720434725</v>
+        <v>0.008580197679360246</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B146" t="n">
@@ -4666,14 +4678,14 @@
         <v>107.90904761905</v>
       </c>
       <c r="H146" t="n">
-        <v>227.842</v>
+        <v>110.04</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7473636856351531</v>
+        <v>-0.01955521541655525</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B147" t="n">
@@ -4695,14 +4707,14 @@
         <v>111.15619047619</v>
       </c>
       <c r="H147" t="n">
-        <v>228.329</v>
+        <v>110.59</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.7198512376599986</v>
+        <v>0.005106664564571872</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B148" t="n">
@@ -4724,18 +4736,18 @@
         <v>119.70238095238</v>
       </c>
       <c r="H148" t="n">
-        <v>228.807</v>
+        <v>111</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.6478703500798071</v>
+        <v>0.07547830205109651</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B149" t="n">
-        <v>-3.768373197178725</v>
+        <v>-3.768373197178724</v>
       </c>
       <c r="C149" t="n">
         <v>3.857750690414038</v>
@@ -4753,14 +4765,14 @@
         <v>124.92863636364</v>
       </c>
       <c r="H149" t="n">
-        <v>229.187</v>
+        <v>111.64</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.6067955990285396</v>
+        <v>0.1124632565126511</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B150" t="n">
@@ -4782,14 +4794,14 @@
         <v>120.4635</v>
       </c>
       <c r="H150" t="n">
-        <v>228.713</v>
+        <v>111.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6411211399574892</v>
+        <v>0.07293722088693855</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B151" t="n">
@@ -4811,14 +4823,14 @@
         <v>110.52173913044</v>
       </c>
       <c r="H151" t="n">
-        <v>228.524</v>
+        <v>112.57</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7264290018211588</v>
+        <v>-0.01836301454641553</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B152" t="n">
@@ -4840,18 +4852,18 @@
         <v>95.58904761905001</v>
       </c>
       <c r="H152" t="n">
-        <v>228.59</v>
+        <v>113.57</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.8718717570319212</v>
+        <v>-0.1723611380635193</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B153" t="n">
-        <v>-0.1021760088819951</v>
+        <v>-0.1021760088819952</v>
       </c>
       <c r="C153" t="n">
         <v>3.742570727008806</v>
@@ -4869,14 +4881,14 @@
         <v>103.14090909091</v>
       </c>
       <c r="H153" t="n">
-        <v>229.918</v>
+        <v>114.97</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.8016266208861627</v>
+        <v>-0.1085751220367319</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B154" t="n">
@@ -4898,14 +4910,14 @@
         <v>113.34</v>
       </c>
       <c r="H154" t="n">
-        <v>231.015</v>
+        <v>115.08</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.7120904927370653</v>
+        <v>-0.01523538794187473</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B155" t="n">
@@ -4927,14 +4939,14 @@
         <v>113.3825</v>
       </c>
       <c r="H155" t="n">
-        <v>231.638</v>
+        <v>115.72</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.7144087498356493</v>
+        <v>-0.02040642171064544</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B156" t="n">
@@ -4956,14 +4968,14 @@
         <v>111.97347826087</v>
       </c>
       <c r="H156" t="n">
-        <v>231.249</v>
+        <v>116.25</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7252330100478392</v>
+        <v>-0.03748100245644448</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B157" t="n">
@@ -4985,14 +4997,14 @@
         <v>109.71181818182</v>
       </c>
       <c r="H157" t="n">
-        <v>231.221</v>
+        <v>116.64</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.7455168698140575</v>
+        <v>-0.06123517495119124</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B158" t="n">
@@ -5014,14 +5026,14 @@
         <v>109.6765</v>
       </c>
       <c r="H158" t="n">
-        <v>231.679</v>
+        <v>117.27</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.7478176691586604</v>
+        <v>-0.06694384474193971</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B159" t="n">
@@ -5043,14 +5055,14 @@
         <v>112.97363636364</v>
       </c>
       <c r="H159" t="n">
-        <v>232.937</v>
+        <v>118.41</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.7236135457629675</v>
+        <v>-0.04699869336718354</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B160" t="n">
@@ -5072,14 +5084,14 @@
         <v>116.5195</v>
       </c>
       <c r="H160" t="n">
-        <v>232.282</v>
+        <v>119.08</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6898935097914922</v>
+        <v>-0.02173689517437083</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B161" t="n">
@@ -5101,14 +5113,14 @@
         <v>109.24</v>
       </c>
       <c r="H161" t="n">
-        <v>231.797</v>
+        <v>119.48</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7523146920248518</v>
+        <v>-0.08960169674240515</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B162" t="n">
@@ -5130,18 +5142,18 @@
         <v>102.87545454546</v>
       </c>
       <c r="H162" t="n">
-        <v>231.893</v>
+        <v>120.09</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.8127569809687873</v>
+        <v>-0.1547223842602348</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B163" t="n">
-        <v>-2.126261964223034</v>
+        <v>-2.126261964223033</v>
       </c>
       <c r="C163" t="n">
         <v>3.73297856993634</v>
@@ -5159,14 +5171,14 @@
         <v>103.02695652174</v>
       </c>
       <c r="H163" t="n">
-        <v>232.445</v>
+        <v>120.88</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.8136629701112463</v>
+        <v>-0.1598076501726311</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B164" t="n">
@@ -5188,14 +5200,14 @@
         <v>103.11</v>
       </c>
       <c r="H164" t="n">
-        <v>232.9</v>
+        <v>121.39</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.8148127973604433</v>
+        <v>-0.1632121233798607</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B165" t="n">
@@ -5217,14 +5229,14 @@
         <v>107.71608695652</v>
       </c>
       <c r="H165" t="n">
-        <v>233.456</v>
+        <v>122.39</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.7734946813008312</v>
+        <v>-0.127713726173412</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B166" t="n">
@@ -5246,14 +5258,14 @@
         <v>110.96454545455</v>
       </c>
       <c r="H166" t="n">
-        <v>233.544</v>
+        <v>122.56</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.744159756217174</v>
+        <v>-0.09938996602165684</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B167" t="n">
@@ -5275,14 +5287,14 @@
         <v>111.62142857143</v>
       </c>
       <c r="H167" t="n">
-        <v>233.669</v>
+        <v>122.81</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.7387925402472781</v>
+        <v>-0.09552540181828295</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B168" t="n">
@@ -5304,14 +5316,14 @@
         <v>109.47869565217</v>
       </c>
       <c r="H168" t="n">
-        <v>234.1</v>
+        <v>123.51</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.760018404423767</v>
+        <v>-0.1205921543768245</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B169" t="n">
@@ -5333,14 +5345,14 @@
         <v>108.07619047619</v>
       </c>
       <c r="H169" t="n">
-        <v>234.719</v>
+        <v>124.21</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.7755526082190167</v>
+        <v>-0.1391372357848875</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B170" t="n">
@@ -5362,14 +5374,14 @@
         <v>110.674</v>
       </c>
       <c r="H170" t="n">
-        <v>235.288</v>
+        <v>124.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.7542213525946186</v>
+        <v>-0.1204439742893912</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B171" t="n">
@@ -5391,14 +5403,14 @@
         <v>107.42</v>
       </c>
       <c r="H171" t="n">
-        <v>235.547</v>
+        <v>125.58</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7851640844381933</v>
+        <v>-0.1561966212086494</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B172" t="n">
@@ -5420,14 +5432,14 @@
         <v>108.81</v>
       </c>
       <c r="H172" t="n">
-        <v>236.028</v>
+        <v>126.45</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.7743472000928353</v>
+        <v>-0.1502437311530533</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B173" t="n">
@@ -5449,14 +5461,14 @@
         <v>107.4</v>
       </c>
       <c r="H173" t="n">
-        <v>236.468</v>
+        <v>127.74</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.7892527101485545</v>
+        <v>-0.1734367660586784</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B174" t="n">
@@ -5478,14 +5490,14 @@
         <v>107.79</v>
       </c>
       <c r="H174" t="n">
-        <v>236.918</v>
+        <v>128.89</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.7875291999115221</v>
+        <v>-0.1787744376231508</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B175" t="n">
@@ -5507,14 +5519,14 @@
         <v>109.68</v>
       </c>
       <c r="H175" t="n">
-        <v>237.231</v>
+        <v>130.05</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.7714673147297972</v>
+        <v>-0.1703519566406024</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B176" t="n">
@@ -5536,14 +5548,14 @@
         <v>111.87</v>
       </c>
       <c r="H176" t="n">
-        <v>237.498</v>
+        <v>130.86</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.752821719527768</v>
+        <v>-0.156790566582754</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B177" t="n">
@@ -5565,14 +5577,14 @@
         <v>106.98</v>
       </c>
       <c r="H177" t="n">
-        <v>237.46</v>
+        <v>131.5</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.7973572871345427</v>
+        <v>-0.2063649505147156</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B178" t="n">
@@ -5594,14 +5606,14 @@
         <v>101.92</v>
       </c>
       <c r="H178" t="n">
-        <v>237.477</v>
+        <v>131.82</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.8458825848560805</v>
+        <v>-0.2572491638007204</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B179" t="n">
@@ -5623,14 +5635,14 @@
         <v>97.34</v>
       </c>
       <c r="H179" t="n">
-        <v>237.43</v>
+        <v>132.67</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.8916628387838426</v>
+        <v>-0.3096548375235173</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B180" t="n">
@@ -5652,14 +5664,14 @@
         <v>87.27</v>
       </c>
       <c r="H180" t="n">
-        <v>236.983</v>
+        <v>133.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.9989816474293889</v>
+        <v>-0.4270403881611715</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B181" t="n">
@@ -5681,10 +5693,10 @@
         <v>78.44</v>
       </c>
       <c r="H181" t="n">
-        <v>236.252</v>
+        <v>135.47</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.102565030618339</v>
+        <v>-0.5464162122645</v>
       </c>
     </row>
   </sheetData>
